--- a/output/thirdVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
+++ b/output/thirdVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
@@ -1159,9 +1159,9 @@
     <comment ref="G8" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】容積率（P002-00 修正百分比）
-填寫值：6.25
+填寫值：-6.25
 資料來源：比準地 P001-00 普通(3) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25
+判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = -6.25
 基準表項目ID：shulin.regional.far</t>
       </text>
     </comment>
@@ -1420,7 +1420,7 @@
     <comment ref="E11" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(1)土地使用管制 百分比小計（P002-00）
-填寫值：6.25
+填寫值：-6.25
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group1</t>
@@ -1483,9 +1483,9 @@
     <comment ref="G12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P002-00 修正百分比）
-填寫值：15.0
+填寫值：-15.0
 資料來源：比準地 P001-00 優(1) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = -15.00
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1510,9 +1510,9 @@
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P003-00 修正百分比）
-填寫值：11.25
+填寫值：-11.25
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1537,9 +1537,9 @@
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】主要道路寬度（P004-00 修正百分比）
-填寫值：11.25
+填寫值：-11.25
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1582,9 +1582,9 @@
     <comment ref="G13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P002-00 修正百分比）
-填寫值：6.0
+填寫值：-6.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1609,9 +1609,9 @@
     <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P003-00 修正百分比）
-填寫值：6.0
+填寫值：-6.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1636,9 +1636,9 @@
     <comment ref="M13" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路平均寬度（P004-00 修正百分比）
-填寫值：6.0
+填寫值：-6.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1681,9 +1681,9 @@
     <comment ref="G14" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近大型車站之程度（P002-00 修正百分比）
-填寫值：-2.5
+填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
 基準表項目ID：shulin.regional.near_station</t>
       </text>
     </comment>
@@ -1834,9 +1834,9 @@
     <comment ref="M15" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】站牌之接近程度或密集程度（P004-00 修正百分比）
-填寫值：1.0
+填寫值：-1.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(2−1)×1.0 = +1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = -1.00
 基準表項目ID：shulin.regional.near_busstop</t>
       </text>
     </comment>
@@ -1933,9 +1933,9 @@
     <comment ref="M16" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】交流道之有無及接近交流道之程度（P004-00 修正百分比）
-填寫值：1.0
+填寫值：-1.0
 資料來源：比準地 P001-00 稍劣(4) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±4.0%、級距1.0%；(5−4)×1.0 = +1.00
+判定依據：查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = -1.00
 基準表項目ID：shulin.regional.near_interchange</t>
       </text>
     </comment>
@@ -1978,9 +1978,9 @@
     <comment ref="G17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P002-00 修正百分比）
-填寫值：2.5
+填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 普通(3)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2005,9 +2005,9 @@
     <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P003-00 修正百分比）
-填寫值：-2.5
+填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -2032,16 +2032,16 @@
     <comment ref="M17" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】區段內道路規劃及闢建程度（P004-00 修正百分比）
-填寫值：-2.5
+填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P004-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P002-00）
-填寫值：21.0
+填寫值：-21.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2050,7 +2050,7 @@
     <comment ref="H18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P003-00）
-填寫值：14.75
+填寫值：-14.75
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2059,7 +2059,7 @@
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(2)交通運輸 百分比小計（P004-00）
-填寫值：16.75
+填寫值：-16.75
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group2</t>
@@ -2851,9 +2851,9 @@
     <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P002-00 修正百分比）
-填寫值：-4.0
+填寫值：4.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -2878,9 +2878,9 @@
     <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P003-00 修正百分比）
-填寫值：-4.0
+填寫值：4.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -2905,9 +2905,9 @@
     <comment ref="M28" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近市場之程度（傳統市場、超級市場、超大型購物中心）（P004-00 修正百分比）
-填寫值：-2.0
+填寫值：2.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(2−3)×2.0 = -2.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = +2.00
 基準表項目ID：shulin.regional.near_market</t>
       </text>
     </comment>
@@ -3004,9 +3004,9 @@
     <comment ref="M29" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近公園（里鄰公園、一般公園）、廣場、徒步區之程度（P004-00 修正百分比）
-填寫值：4.0
+填寫值：-4.0
 資料來源：比準地 P001-00 優(1) ／ P004-00 普通(3)
-判定依據：查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00
+判定依據：查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00
 基準表項目ID：shulin.regional.near_park</t>
       </text>
     </comment>
@@ -3049,9 +3049,9 @@
     <comment ref="G30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P002-00 修正百分比）
-填寫值：1.5
+填寫值：-1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3076,9 +3076,9 @@
     <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P003-00 修正百分比）
-填寫值：1.5
+填寫值：-1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3103,9 +3103,9 @@
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】接近觀光遊憩設施之程度（P004-00 修正百分比）
-填寫值：1.5
+填寫值：-1.5
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
 基準表項目ID：shulin.regional.near_tourism</t>
       </text>
     </comment>
@@ -3148,9 +3148,9 @@
     <comment ref="G31" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】停車場地之便利程度（P002-00 修正百分比）
-填寫值：1.5
+填寫值：-1.5
 資料來源：比準地 P001-00 優(1) ／ P002-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3175,9 +3175,9 @@
     <comment ref="J31" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】停車場地之便利程度（P003-00 修正百分比）
-填寫值：1.5
+填寫值：-1.5
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍優(2)
-判定依據：查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50
+判定依據：查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50
 基準表項目ID：shulin.regional.parking</t>
       </text>
     </comment>
@@ -3310,7 +3310,7 @@
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P002-00）
-填寫值：-1.0
+填寫值：1.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -3319,7 +3319,7 @@
     <comment ref="H33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P003-00）
-填寫值：-1.0
+填寫值：1.0
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -3328,7 +3328,7 @@
     <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>【AI判定】(5)公共建設 百分比小計（P004-00）
-填寫值：3.5
+填寫值：-3.5
 資料來源：本表同組各修正細項修正百分比
 判定依據：＝該主要項目全部細項修正百分比之和
 基準表項目ID：shulin.regional.group5</t>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="G8" s="68" t="n">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="H8" s="72" t="n">
         <v>3</v>
@@ -5217,7 +5217,7 @@
       <c r="C11" s="65" t="n"/>
       <c r="D11" s="60" t="n"/>
       <c r="E11" s="78" t="n">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="F11" s="63" t="n"/>
       <c r="G11" s="36" t="inlineStr">
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="G12" s="75" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="H12" s="74" t="n">
         <v>4</v>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="J12" s="75" t="n">
-        <v>11.25</v>
+        <v>-11.25</v>
       </c>
       <c r="K12" s="74" t="n">
         <v>4</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="M12" s="75" t="n">
-        <v>11.25</v>
+        <v>-11.25</v>
       </c>
       <c r="N12" s="13" t="n"/>
       <c r="O12" s="6" t="n"/>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="G13" s="75" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="H13" s="74" t="n">
         <v>5</v>
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="J13" s="75" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="K13" s="74" t="n">
         <v>5</v>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="M13" s="75" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="N13" s="13" t="n"/>
       <c r="O13" s="6" t="n"/>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="G14" s="75" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="H14" s="74" t="n">
         <v>2</v>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="M15" s="75" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N15" s="13" t="n"/>
       <c r="O15" s="6" t="n"/>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M16" s="75" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N16" s="13" t="n"/>
       <c r="O16" s="6" t="n"/>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="G17" s="75" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H17" s="74" t="n">
         <v>1</v>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="J17" s="75" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="K17" s="74" t="n">
         <v>1</v>
@@ -5563,7 +5563,7 @@
         </is>
       </c>
       <c r="M17" s="75" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="N17" s="13" t="n"/>
       <c r="O17" s="6" t="n"/>
@@ -5580,7 +5580,7 @@
       <c r="C18" s="65" t="n"/>
       <c r="D18" s="60" t="n"/>
       <c r="E18" s="78" t="n">
-        <v>21</v>
+        <v>-21</v>
       </c>
       <c r="F18" s="63" t="n"/>
       <c r="G18" s="36" t="inlineStr">
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="H18" s="78" t="n">
-        <v>14.75</v>
+        <v>-14.75</v>
       </c>
       <c r="I18" s="63" t="n"/>
       <c r="J18" s="36" t="inlineStr">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="K18" s="78" t="n">
-        <v>16.75</v>
+        <v>-16.75</v>
       </c>
       <c r="L18" s="63" t="n"/>
       <c r="M18" s="36" t="inlineStr">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="G28" s="75" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="H28" s="74" t="n">
         <v>1</v>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="J28" s="75" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="K28" s="74" t="n">
         <v>2</v>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="M28" s="75" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="N28" s="13" t="n"/>
       <c r="O28" s="6" t="n"/>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="M29" s="75" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="N29" s="13" t="n"/>
       <c r="O29" s="6" t="n"/>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="G30" s="75" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H30" s="74" t="n">
         <v>2</v>
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="J30" s="75" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="K30" s="74" t="n">
         <v>2</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="M30" s="75" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="N30" s="13" t="n"/>
       <c r="O30" s="6" t="n"/>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G31" s="75" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H31" s="74" t="n">
         <v>2</v>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="J31" s="75" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="K31" s="74" t="n">
         <v>1</v>
@@ -6351,7 +6351,7 @@
       <c r="C33" s="65" t="n"/>
       <c r="D33" s="60" t="n"/>
       <c r="E33" s="78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F33" s="63" t="n"/>
       <c r="G33" s="36" t="inlineStr">
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="H33" s="78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I33" s="63" t="n"/>
       <c r="J33" s="36" t="inlineStr">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="K33" s="78" t="n">
-        <v>3.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L33" s="63" t="n"/>
       <c r="M33" s="36" t="inlineStr">
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25</t>
+          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = -6.25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -10269,7 +10269,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = -15.00</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.25</v>
+        <v>-11.25</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.25</v>
+        <v>-11.25</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = -11.25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10717,7 +10717,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -10961,7 +10961,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = -6.00</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -11857,7 +11857,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(2−1)×1.0 = +1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(1−2)×1.0 = -1.00</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±4.0%、級距1.0%；(5−4)×1.0 = +1.00</t>
+          <t>查表：共5級、最大±4.0%、級距1.0%；(4−5)×1.0 = -1.00</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12509,7 +12509,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(2−3)×2.0 = -2.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(3−2)×2.0 = +2.00</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -16785,7 +16785,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±8.0%、級距2.0%；(3−1)×2.0 = +4.00</t>
+          <t>查表：共5級、最大±8.0%、級距2.0%；(1−3)×2.0 = -4.00</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -17111,7 +17111,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -17233,7 +17233,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -17437,7 +17437,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -17559,7 +17559,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±6.0%、級距1.5%；(2−1)×1.5 = +1.50</t>
+          <t>查表：共5級、最大±6.0%、級距1.5%；(1−2)×1.5 = -1.50</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -19577,7 +19577,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>21</v>
+        <v>-21</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>14.75</v>
+        <v>-14.75</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>16.75</v>
+        <v>-16.75</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>3.5</v>
+        <v>-3.5</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
